--- a/Maret 2026/Analisis Gempabumi Periode Maret 2026.xlsx
+++ b/Maret 2026/Analisis Gempabumi Periode Maret 2026.xlsx
@@ -32259,12 +32259,12 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>M&lt;3</t>
+          <t>M≤3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>3≤M&lt;5</t>
+          <t>3&lt;M&lt;5</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -32470,10 +32470,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -32495,10 +32495,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -32545,10 +32545,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -32895,10 +32895,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -33045,10 +33045,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -33070,10 +33070,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="C33" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -33401,10 +33401,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -33926,10 +33926,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C33" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
